--- a/site/ns_leads.xlsx
+++ b/site/ns_leads.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nova Scotia" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Nova Scotia" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/site/ns_leads.xlsx
+++ b/site/ns_leads.xlsx
@@ -6510,12 +6510,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Castle Frederick Pb, Zn, Ag Occurrence</t>
+          <t>MacLeods Lake Au Occurrence</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>A16-039</t>
+          <t>K07-060</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
@@ -6527,12 +6527,12 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Pb, Zn, Ag, Ba, As</t>
+          <t>Au, Cu, Ag</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Boulder</t>
         </is>
       </c>
       <c r="I80" t="b">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>Pb 24.2%, Ag 39.60 g/t, Zn 1.89%, Be 0.00022%, Bi 0.000165%</t>
+          <t>Au 4.26 g/t, Co 0.0012%, Cr 0.0069%, Cu 0.0255%, Li 0.0012%</t>
         </is>
       </c>
       <c r="M80" t="inlineStr"/>
@@ -6569,14 +6569,14 @@
         <v>36</v>
       </c>
       <c r="V80" t="n">
-        <v>44.93124</v>
+        <v>46.27323</v>
       </c>
       <c r="W80" t="n">
-        <v>-64.24603</v>
+        <v>-60.69898</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A16-039</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-060</t>
         </is>
       </c>
     </row>
@@ -6586,12 +6586,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Lake Ainslie Barite-Fluorite Deposits</t>
+          <t>Castle Frederick Pb, Zn, Ag Occurrence</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>K03-035</t>
+          <t>A16-039</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -6603,12 +6603,12 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Ba, F</t>
+          <t>Pb, Zn, Ag, Ba, As</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I81" t="b">
@@ -6622,7 +6622,11 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr"/>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>Pb 24.2%, Ag 39.60 g/t, Zn 1.89%, Be 0.00022%, Bi 0.000165%</t>
+        </is>
+      </c>
       <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
       <c r="O81" t="n">
@@ -6638,17 +6642,17 @@
         <v>325</v>
       </c>
       <c r="U81" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="V81" t="n">
-        <v>46.19675</v>
+        <v>44.93124</v>
       </c>
       <c r="W81" t="n">
-        <v>-61.17421</v>
+        <v>-64.24603</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K03-035</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A16-039</t>
         </is>
       </c>
     </row>
@@ -6713,10 +6717,10 @@
         <v>35</v>
       </c>
       <c r="V82" t="n">
-        <v>46.21501</v>
+        <v>46.19675</v>
       </c>
       <c r="W82" t="n">
-        <v>-61.11267</v>
+        <v>-61.17421</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -6730,12 +6734,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>McCuish Mn Mine</t>
+          <t>Lake Ainslie Barite-Fluorite Deposits</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>F15-009</t>
+          <t>K03-035</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -6747,7 +6751,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Ba, F</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -6785,14 +6789,14 @@
         <v>35</v>
       </c>
       <c r="V83" t="n">
-        <v>45.80966</v>
+        <v>46.21501</v>
       </c>
       <c r="W83" t="n">
-        <v>-60.50423</v>
+        <v>-61.11267</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K03-035</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6806,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Yava Pb Deposit (Silvermine Pb Deposit)</t>
+          <t>McCuish Mn Mine</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>F16-025</t>
+          <t>F15-009</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -6819,7 +6823,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Pb, Zn, Cu</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -6857,14 +6861,14 @@
         <v>35</v>
       </c>
       <c r="V84" t="n">
-        <v>45.86575</v>
+        <v>45.80966</v>
       </c>
       <c r="W84" t="n">
-        <v>-60.40045</v>
+        <v>-60.50423</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F16-025</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-009</t>
         </is>
       </c>
     </row>
@@ -6929,10 +6933,10 @@
         <v>35</v>
       </c>
       <c r="V85" t="n">
-        <v>45.86017</v>
+        <v>45.86575</v>
       </c>
       <c r="W85" t="n">
-        <v>-60.4163</v>
+        <v>-60.40045</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -7001,10 +7005,10 @@
         <v>35</v>
       </c>
       <c r="V86" t="n">
-        <v>45.87077</v>
+        <v>45.86017</v>
       </c>
       <c r="W86" t="n">
-        <v>-60.38759</v>
+        <v>-60.4163</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -7018,12 +7022,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Upper Glencoe Fe Deposit</t>
+          <t>Yava Pb Deposit (Silvermine Pb Deposit)</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>F14-007</t>
+          <t>F16-025</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
@@ -7035,7 +7039,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Fe, Cu</t>
+          <t>Pb, Zn, Cu</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -7073,14 +7077,14 @@
         <v>35</v>
       </c>
       <c r="V87" t="n">
-        <v>45.92081</v>
+        <v>45.87077</v>
       </c>
       <c r="W87" t="n">
-        <v>-61.3156</v>
+        <v>-60.38759</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F14-007</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F16-025</t>
         </is>
       </c>
     </row>
@@ -7090,12 +7094,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>McCuish Mn Mine</t>
+          <t>Upper Glencoe Fe Deposit</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>F15-009</t>
+          <t>F14-007</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
@@ -7107,7 +7111,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>Fe, Cu</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -7145,14 +7149,14 @@
         <v>35</v>
       </c>
       <c r="V88" t="n">
-        <v>45.80981</v>
+        <v>45.92081</v>
       </c>
       <c r="W88" t="n">
-        <v>-60.50294</v>
+        <v>-61.3156</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-009</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F14-007</t>
         </is>
       </c>
     </row>
@@ -7162,12 +7166,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>MacLeods Lake Au Occurrence</t>
+          <t>McCuish Mn Mine</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>K07-060</t>
+          <t>F15-009</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
@@ -7179,12 +7183,12 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Au, Cu, Ag</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Boulder</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I89" t="b">
@@ -7198,11 +7202,7 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>Au 4.26 g/t, Co 0.0012%, Cr 0.0069%, Cu 0.0255%, Li 0.0012%</t>
-        </is>
-      </c>
+      <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
       <c r="O89" t="n">
@@ -7221,14 +7221,14 @@
         <v>35</v>
       </c>
       <c r="V89" t="n">
-        <v>46.27323</v>
+        <v>45.80981</v>
       </c>
       <c r="W89" t="n">
-        <v>-60.69898</v>
+        <v>-60.50294</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-060</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F15-009</t>
         </is>
       </c>
     </row>

--- a/site/ns_leads.xlsx
+++ b/site/ns_leads.xlsx
@@ -7974,12 +7974,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>New Russell Mo Prospect (Walker Moly)</t>
+          <t>C. B. Highlands (Zone 13 A &amp; B Trenches) Au Occurrence</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>A16-033</t>
+          <t>K10-066</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
@@ -7991,12 +7991,12 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>F, Mo, Cu, Sn, W</t>
+          <t>Au, Cu, Ag</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I100" t="b">
@@ -8012,7 +8012,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>Cu 2.04%, Pb 0.0032%, Zn 0.0207%</t>
+          <t>Au 3.98 g/t, Ag 7.80 g/t, Be 0.0001%, Bi 0.00072%, Co 0.00052%</t>
         </is>
       </c>
       <c r="M100" t="inlineStr"/>
@@ -8030,17 +8030,17 @@
         <v>325</v>
       </c>
       <c r="U100" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="V100" t="n">
-        <v>44.77299</v>
+        <v>46.52383</v>
       </c>
       <c r="W100" t="n">
-        <v>-64.41443</v>
+        <v>-60.71507</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A16-033</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-066</t>
         </is>
       </c>
     </row>
@@ -8106,13 +8106,13 @@
         <v>325</v>
       </c>
       <c r="U101" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="V101" t="n">
-        <v>46.52383</v>
+        <v>46.52503</v>
       </c>
       <c r="W101" t="n">
-        <v>-60.71507</v>
+        <v>-60.71296</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -8126,12 +8126,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>C. B. Highlands (Zone 13 A &amp; B Trenches) Au Occurrence</t>
+          <t>New Russell Mo Prospect (Walker Moly)</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>K10-066</t>
+          <t>A16-033</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
@@ -8143,12 +8143,12 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Au, Cu, Ag</t>
+          <t>F, Mo, Cu, Sn, W</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I102" t="b">
@@ -8164,7 +8164,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>Au 3.98 g/t, Ag 7.80 g/t, Be 0.0001%, Bi 0.00072%, Co 0.00052%</t>
+          <t>Cu 2.04%, Pb 0.0032%, Zn 0.0207%</t>
         </is>
       </c>
       <c r="M102" t="inlineStr"/>
@@ -8185,14 +8185,14 @@
         <v>33</v>
       </c>
       <c r="V102" t="n">
-        <v>46.52503</v>
+        <v>44.77299</v>
       </c>
       <c r="W102" t="n">
-        <v>-60.71296</v>
+        <v>-64.41443</v>
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-066</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A16-033</t>
         </is>
       </c>
     </row>
@@ -22766,12 +22766,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>East Dalhousie Cu, Sn, Li, Zn, Ag, As Prospect</t>
+          <t>Grand Lake Au, Ag Prospect</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>A10-001</t>
+          <t>D13-006</t>
         </is>
       </c>
       <c r="D304" t="inlineStr"/>
@@ -22783,7 +22783,7 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Sn, Cu, Li, Zn, Ag, As</t>
+          <t>Au, Ag</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -22804,7 +22804,7 @@
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t>Sn 0.0732%, Cu 0.143%, Ag 5.70 g/t, Be 0.00024%, Bi 0.00317%</t>
+          <t>Au 0.80 g/t, Ag 6.00 g/t, W 0.0004%, Zn 0.0054%</t>
         </is>
       </c>
       <c r="M304" t="inlineStr"/>
@@ -22822,17 +22822,17 @@
         <v>325</v>
       </c>
       <c r="U304" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="V304" t="n">
-        <v>44.71912</v>
+        <v>44.87004</v>
       </c>
       <c r="W304" t="n">
-        <v>-64.79982</v>
+        <v>-63.63384</v>
       </c>
       <c r="X304" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A10-001</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D13-006</t>
         </is>
       </c>
     </row>
@@ -22842,12 +22842,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Grand Lake Au, Ag Prospect</t>
+          <t>Taylors Brook  Au, Cu, Zn Occurrence</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>D13-006</t>
+          <t>F10-003</t>
         </is>
       </c>
       <c r="D305" t="inlineStr"/>
@@ -22859,12 +22859,12 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Au, Ag</t>
+          <t>Au, Cu, Zn</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I305" t="b">
@@ -22880,7 +22880,7 @@
       </c>
       <c r="L305" t="inlineStr">
         <is>
-          <t>Au 0.80 g/t, Ag 6.00 g/t, W 0.0004%, Zn 0.0054%</t>
+          <t>Cu 1.51%, Au 0.63 g/t, Ag 2.70 g/t, Co 0.006%, Cr 0.0075%</t>
         </is>
       </c>
       <c r="M305" t="inlineStr"/>
@@ -22901,14 +22901,14 @@
         <v>28</v>
       </c>
       <c r="V305" t="n">
-        <v>44.87004</v>
+        <v>45.66139</v>
       </c>
       <c r="W305" t="n">
-        <v>-63.63384</v>
+        <v>-60.50763</v>
       </c>
       <c r="X305" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D13-006</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F10-003</t>
         </is>
       </c>
     </row>
@@ -22918,12 +22918,12 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Kenney Shore Sn, Cu Skarn</t>
+          <t>East Dalhousie Cu, Sn, Li, Zn, Ag, As Prospect</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>A05-005</t>
+          <t>A10-001</t>
         </is>
       </c>
       <c r="D306" t="inlineStr"/>
@@ -22935,12 +22935,12 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Sn, Cu</t>
+          <t>Sn, Cu, Li, Zn, Ag, As</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I306" t="b">
@@ -22956,7 +22956,7 @@
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t>Sn 0.497%, Cu 0.17%, Ag 2.50 g/t, Be 0.00063%, Bi 0.00121%</t>
+          <t>Sn 0.0732%, Cu 0.143%, Ag 5.70 g/t, Be 0.00024%, Bi 0.00317%</t>
         </is>
       </c>
       <c r="M306" t="inlineStr"/>
@@ -22974,17 +22974,17 @@
         <v>325</v>
       </c>
       <c r="U306" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="V306" t="n">
-        <v>44.48487</v>
+        <v>44.71912</v>
       </c>
       <c r="W306" t="n">
-        <v>-65.96890999999999</v>
+        <v>-64.79982</v>
       </c>
       <c r="X306" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A05-005</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A10-001</t>
         </is>
       </c>
     </row>
@@ -22994,12 +22994,12 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Triangle Cu, Pb, Zn, Ag, Au Showings</t>
+          <t>Taylors Brook  Au, Cu, Zn Occurrence</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>K10-024</t>
+          <t>F10-003</t>
         </is>
       </c>
       <c r="D307" t="inlineStr"/>
@@ -23011,12 +23011,12 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Ag, As, Au, Bi, Cu, Pb, Zn</t>
+          <t>Au, Cu, Zn</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I307" t="b">
@@ -23032,7 +23032,7 @@
       </c>
       <c r="L307" t="inlineStr">
         <is>
-          <t>Ag 25.00 g/t, Bi 0.0216%, Au 0.21 g/t, Cd 0.00211%, Co 0.005%</t>
+          <t>Cu 1.51%, Au 0.63 g/t, Ag 2.70 g/t, Co 0.006%, Cr 0.0075%</t>
         </is>
       </c>
       <c r="M307" t="inlineStr"/>
@@ -23050,17 +23050,17 @@
         <v>325</v>
       </c>
       <c r="U307" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="V307" t="n">
-        <v>46.60835</v>
+        <v>45.66247</v>
       </c>
       <c r="W307" t="n">
-        <v>-60.92328</v>
+        <v>-60.50348</v>
       </c>
       <c r="X307" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-024</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F10-003</t>
         </is>
       </c>
     </row>
@@ -23070,12 +23070,12 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Triangle Cu, Pb, Zn, Ag, Au Showings</t>
+          <t>Taylors Brook  Au, Cu, Zn Occurrence</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>K10-024</t>
+          <t>F10-003</t>
         </is>
       </c>
       <c r="D308" t="inlineStr"/>
@@ -23087,12 +23087,12 @@
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Ag, As, Au, Bi, Cu, Pb, Zn</t>
+          <t>Au, Cu, Zn</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I308" t="b">
@@ -23108,7 +23108,7 @@
       </c>
       <c r="L308" t="inlineStr">
         <is>
-          <t>Ag 25.00 g/t, Bi 0.0216%, Au 0.21 g/t, Cd 0.00211%, Co 0.005%</t>
+          <t>Cu 1.51%, Au 0.63 g/t, Ag 2.70 g/t, Co 0.006%, Cr 0.0075%</t>
         </is>
       </c>
       <c r="M308" t="inlineStr"/>
@@ -23126,17 +23126,17 @@
         <v>325</v>
       </c>
       <c r="U308" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="V308" t="n">
-        <v>46.60665</v>
+        <v>45.66068</v>
       </c>
       <c r="W308" t="n">
-        <v>-60.92386</v>
+        <v>-60.49983</v>
       </c>
       <c r="X308" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-024</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F10-003</t>
         </is>
       </c>
     </row>
@@ -23146,12 +23146,12 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Triangle Cu, Pb, Zn, Ag, Au Showings</t>
+          <t>Kenney Shore Sn, Cu Skarn</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>K10-024</t>
+          <t>A05-005</t>
         </is>
       </c>
       <c r="D309" t="inlineStr"/>
@@ -23163,12 +23163,12 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Ag, As, Au, Bi, Cu, Pb, Zn</t>
+          <t>Sn, Cu</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I309" t="b">
@@ -23184,7 +23184,7 @@
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t>Ag 25.00 g/t, Bi 0.0216%, Au 0.21 g/t, Cd 0.00211%, Co 0.005%</t>
+          <t>Sn 0.497%, Cu 0.17%, Ag 2.50 g/t, Be 0.00063%, Bi 0.00121%</t>
         </is>
       </c>
       <c r="M309" t="inlineStr"/>
@@ -23205,14 +23205,14 @@
         <v>27</v>
       </c>
       <c r="V309" t="n">
-        <v>46.60547</v>
+        <v>44.48487</v>
       </c>
       <c r="W309" t="n">
-        <v>-60.92313</v>
+        <v>-65.96890999999999</v>
       </c>
       <c r="X309" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-024</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=A05-005</t>
         </is>
       </c>
     </row>
@@ -23602,12 +23602,12 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>Triangle Cu, Pb, Zn, Ag, Au Showings</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>K10-024</t>
         </is>
       </c>
       <c r="D315" t="inlineStr"/>
@@ -23619,12 +23619,12 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Ag, As, Au, Bi, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I315" t="b">
@@ -23640,7 +23640,7 @@
       </c>
       <c r="L315" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Ag 25.00 g/t, Bi 0.0216%, Au 0.21 g/t, Cd 0.00211%, Co 0.005%</t>
         </is>
       </c>
       <c r="M315" t="inlineStr"/>
@@ -23661,14 +23661,14 @@
         <v>27</v>
       </c>
       <c r="V315" t="n">
-        <v>46.44956</v>
+        <v>46.60835</v>
       </c>
       <c r="W315" t="n">
-        <v>-60.57775</v>
+        <v>-60.92328</v>
       </c>
       <c r="X315" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-024</t>
         </is>
       </c>
     </row>
@@ -23678,12 +23678,12 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>Triangle Cu, Pb, Zn, Ag, Au Showings</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>K10-024</t>
         </is>
       </c>
       <c r="D316" t="inlineStr"/>
@@ -23695,12 +23695,12 @@
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Ag, As, Au, Bi, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I316" t="b">
@@ -23716,7 +23716,7 @@
       </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Ag 25.00 g/t, Bi 0.0216%, Au 0.21 g/t, Cd 0.00211%, Co 0.005%</t>
         </is>
       </c>
       <c r="M316" t="inlineStr"/>
@@ -23737,14 +23737,14 @@
         <v>27</v>
       </c>
       <c r="V316" t="n">
-        <v>46.44219</v>
+        <v>46.60665</v>
       </c>
       <c r="W316" t="n">
-        <v>-60.58706</v>
+        <v>-60.92386</v>
       </c>
       <c r="X316" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-024</t>
         </is>
       </c>
     </row>
@@ -23754,12 +23754,12 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
+          <t>Triangle Cu, Pb, Zn, Ag, Au Showings</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>K07-061</t>
+          <t>K10-024</t>
         </is>
       </c>
       <c r="D317" t="inlineStr"/>
@@ -23771,12 +23771,12 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>Au, Ag, Cu, Te, Bi, Mo</t>
+          <t>Ag, As, Au, Bi, Cu, Pb, Zn</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I317" t="b">
@@ -23792,7 +23792,7 @@
       </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
+          <t>Ag 25.00 g/t, Bi 0.0216%, Au 0.21 g/t, Cd 0.00211%, Co 0.005%</t>
         </is>
       </c>
       <c r="M317" t="inlineStr"/>
@@ -23813,14 +23813,14 @@
         <v>27</v>
       </c>
       <c r="V317" t="n">
-        <v>46.44885</v>
+        <v>46.60547</v>
       </c>
       <c r="W317" t="n">
-        <v>-60.58676</v>
+        <v>-60.92313</v>
       </c>
       <c r="X317" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K10-024</t>
         </is>
       </c>
     </row>
@@ -23982,12 +23982,12 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Taylors Brook  Au, Cu, Zn Occurrence</t>
+          <t>Lake Ainslie (MacPhails Brook) Pb, Zn Prospect</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>F10-003</t>
+          <t>K03-010</t>
         </is>
       </c>
       <c r="D320" t="inlineStr"/>
@@ -23999,12 +23999,12 @@
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>Au, Cu, Zn</t>
+          <t>Pb, Zn, Cu</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I320" t="b">
@@ -24020,7 +24020,7 @@
       </c>
       <c r="L320" t="inlineStr">
         <is>
-          <t>Cu 1.51%, Au 0.63 g/t, Ag 2.70 g/t, Co 0.006%, Cr 0.0075%</t>
+          <t>Zn 1.02%, Pb 1%, Te 0.0018%, Ag 3.50 g/t, Cd 0.0261%</t>
         </is>
       </c>
       <c r="M320" t="inlineStr"/>
@@ -24041,14 +24041,14 @@
         <v>27</v>
       </c>
       <c r="V320" t="n">
-        <v>45.66068</v>
+        <v>46.1291</v>
       </c>
       <c r="W320" t="n">
-        <v>-60.49983</v>
+        <v>-61.13192</v>
       </c>
       <c r="X320" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F10-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K03-010</t>
         </is>
       </c>
     </row>
@@ -24058,12 +24058,12 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Taylors Brook  Au, Cu, Zn Occurrence</t>
+          <t>Lake Ainslie (MacPhails Brook) Pb, Zn Prospect</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>F10-003</t>
+          <t>K03-010</t>
         </is>
       </c>
       <c r="D321" t="inlineStr"/>
@@ -24075,12 +24075,12 @@
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>Au, Cu, Zn</t>
+          <t>Pb, Zn, Cu</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I321" t="b">
@@ -24096,7 +24096,7 @@
       </c>
       <c r="L321" t="inlineStr">
         <is>
-          <t>Cu 1.51%, Au 0.63 g/t, Ag 2.70 g/t, Co 0.006%, Cr 0.0075%</t>
+          <t>Zn 1.02%, Pb 1%, Te 0.0018%, Ag 3.50 g/t, Cd 0.0261%</t>
         </is>
       </c>
       <c r="M321" t="inlineStr"/>
@@ -24117,14 +24117,14 @@
         <v>27</v>
       </c>
       <c r="V321" t="n">
-        <v>45.66247</v>
+        <v>46.12375</v>
       </c>
       <c r="W321" t="n">
-        <v>-60.50348</v>
+        <v>-61.13508</v>
       </c>
       <c r="X321" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F10-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K03-010</t>
         </is>
       </c>
     </row>
@@ -24134,12 +24134,12 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Taylors Brook  Au, Cu, Zn Occurrence</t>
+          <t>Lake Ainslie (MacPhails Brook) Pb, Zn Prospect</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>F10-003</t>
+          <t>K03-010</t>
         </is>
       </c>
       <c r="D322" t="inlineStr"/>
@@ -24151,12 +24151,12 @@
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>Au, Cu, Zn</t>
+          <t>Pb, Zn, Cu</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Prospect</t>
         </is>
       </c>
       <c r="I322" t="b">
@@ -24172,7 +24172,7 @@
       </c>
       <c r="L322" t="inlineStr">
         <is>
-          <t>Cu 1.51%, Au 0.63 g/t, Ag 2.70 g/t, Co 0.006%, Cr 0.0075%</t>
+          <t>Zn 1.02%, Pb 1%, Te 0.0018%, Ag 3.50 g/t, Cd 0.0261%</t>
         </is>
       </c>
       <c r="M322" t="inlineStr"/>
@@ -24193,14 +24193,14 @@
         <v>27</v>
       </c>
       <c r="V322" t="n">
-        <v>45.66139</v>
+        <v>46.12968</v>
       </c>
       <c r="W322" t="n">
-        <v>-60.50763</v>
+        <v>-61.12853</v>
       </c>
       <c r="X322" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=F10-003</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K03-010</t>
         </is>
       </c>
     </row>
@@ -24210,12 +24210,12 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Lake Ainslie (MacPhails Brook) Pb, Zn Prospect</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>K03-010</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D323" t="inlineStr"/>
@@ -24227,12 +24227,12 @@
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>Pb, Zn, Cu</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I323" t="b">
@@ -24248,7 +24248,7 @@
       </c>
       <c r="L323" t="inlineStr">
         <is>
-          <t>Zn 1.02%, Pb 1%, Te 0.0018%, Ag 3.50 g/t, Cd 0.0261%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M323" t="inlineStr"/>
@@ -24269,14 +24269,14 @@
         <v>27</v>
       </c>
       <c r="V323" t="n">
-        <v>46.12375</v>
+        <v>46.44956</v>
       </c>
       <c r="W323" t="n">
-        <v>-61.13508</v>
+        <v>-60.57775</v>
       </c>
       <c r="X323" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K03-010</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -24286,12 +24286,12 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Lake Ainslie (MacPhails Brook) Pb, Zn Prospect</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>K03-010</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D324" t="inlineStr"/>
@@ -24303,12 +24303,12 @@
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>Pb, Zn, Cu</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I324" t="b">
@@ -24324,7 +24324,7 @@
       </c>
       <c r="L324" t="inlineStr">
         <is>
-          <t>Zn 1.02%, Pb 1%, Te 0.0018%, Ag 3.50 g/t, Cd 0.0261%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M324" t="inlineStr"/>
@@ -24345,14 +24345,14 @@
         <v>27</v>
       </c>
       <c r="V324" t="n">
-        <v>46.1291</v>
+        <v>46.44219</v>
       </c>
       <c r="W324" t="n">
-        <v>-61.13192</v>
+        <v>-60.58706</v>
       </c>
       <c r="X324" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K03-010</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -24362,12 +24362,12 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Lake Ainslie (MacPhails Brook) Pb, Zn Prospect</t>
+          <t>West Branch Indian Brook Au, Ag, Te Occurrence</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>K03-010</t>
+          <t>K07-061</t>
         </is>
       </c>
       <c r="D325" t="inlineStr"/>
@@ -24379,12 +24379,12 @@
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>Pb, Zn, Cu</t>
+          <t>Au, Ag, Cu, Te, Bi, Mo</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I325" t="b">
@@ -24400,7 +24400,7 @@
       </c>
       <c r="L325" t="inlineStr">
         <is>
-          <t>Zn 1.02%, Pb 1%, Te 0.0018%, Ag 3.50 g/t, Cd 0.0261%</t>
+          <t>Au 1.11 g/t, Te 0.0012%, Ag 1.20 g/t, Cu 0.0847%</t>
         </is>
       </c>
       <c r="M325" t="inlineStr"/>
@@ -24421,14 +24421,14 @@
         <v>27</v>
       </c>
       <c r="V325" t="n">
-        <v>46.12968</v>
+        <v>46.44885</v>
       </c>
       <c r="W325" t="n">
-        <v>-61.12853</v>
+        <v>-60.58676</v>
       </c>
       <c r="X325" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K03-010</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-061</t>
         </is>
       </c>
     </row>
@@ -26566,12 +26566,12 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Red River Au Occurrence</t>
+          <t>Doyle Road North Au-Ag Occurrence</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>K15-011</t>
+          <t>K07-078</t>
         </is>
       </c>
       <c r="D354" t="inlineStr"/>
@@ -26583,12 +26583,12 @@
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>Au</t>
+          <t>Au, Ag</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Float</t>
         </is>
       </c>
       <c r="I354" t="b">
@@ -26604,7 +26604,7 @@
       </c>
       <c r="L354" t="inlineStr">
         <is>
-          <t>Au 1.33 g/t</t>
+          <t>Au 1.15 g/t, Ag 8.20 g/t, Bi 0.00238%, Co 0.00318%, Cu 0.0036%</t>
         </is>
       </c>
       <c r="M354" t="inlineStr"/>
@@ -26625,14 +26625,14 @@
         <v>24</v>
       </c>
       <c r="V354" t="n">
-        <v>46.8323</v>
+        <v>46.49086</v>
       </c>
       <c r="W354" t="n">
-        <v>-60.6939</v>
+        <v>-60.73209</v>
       </c>
       <c r="X354" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K15-011</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-078</t>
         </is>
       </c>
     </row>
@@ -26698,13 +26698,13 @@
         <v>325</v>
       </c>
       <c r="U355" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="V355" t="n">
-        <v>46.49086</v>
+        <v>46.488</v>
       </c>
       <c r="W355" t="n">
-        <v>-60.73209</v>
+        <v>-60.74453</v>
       </c>
       <c r="X355" t="inlineStr">
         <is>
@@ -26718,12 +26718,12 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Bridgeville Barite Occurrence</t>
+          <t>Red River Au Occurrence</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>E07-039</t>
+          <t>K15-011</t>
         </is>
       </c>
       <c r="D356" t="inlineStr"/>
@@ -26735,12 +26735,12 @@
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>Ba, Fe, Mn, Cu</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>Float</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I356" t="b">
@@ -26756,7 +26756,7 @@
       </c>
       <c r="L356" t="inlineStr">
         <is>
-          <t>Cu 1.1%, Pb 0.101%, Zn 0.206%</t>
+          <t>Au 1.33 g/t</t>
         </is>
       </c>
       <c r="M356" t="inlineStr"/>
@@ -26774,17 +26774,17 @@
         <v>325</v>
       </c>
       <c r="U356" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="V356" t="n">
-        <v>45.43521</v>
+        <v>46.8323</v>
       </c>
       <c r="W356" t="n">
-        <v>-62.59763</v>
+        <v>-60.6939</v>
       </c>
       <c r="X356" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-039</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K15-011</t>
         </is>
       </c>
     </row>
@@ -26794,12 +26794,12 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Mullach Brook Cu Occurrence</t>
+          <t>Bridgeville Barite Occurrence</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>K03-037</t>
+          <t>E07-039</t>
         </is>
       </c>
       <c r="D357" t="inlineStr"/>
@@ -26811,12 +26811,12 @@
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>Cu, As</t>
+          <t>Ba, Fe, Mn, Cu</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Float</t>
         </is>
       </c>
       <c r="I357" t="b">
@@ -26832,7 +26832,7 @@
       </c>
       <c r="L357" t="inlineStr">
         <is>
-          <t>Cu 0.972%, Au 0.24 g/t</t>
+          <t>Cu 1.1%, Pb 0.101%, Zn 0.206%</t>
         </is>
       </c>
       <c r="M357" t="inlineStr"/>
@@ -26844,23 +26844,23 @@
       <c r="Q357" t="inlineStr"/>
       <c r="R357" t="inlineStr"/>
       <c r="S357" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T357" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U357" t="n">
         <v>23</v>
       </c>
       <c r="V357" t="n">
-        <v>46.00426</v>
+        <v>45.43521</v>
       </c>
       <c r="W357" t="n">
-        <v>-61.11223</v>
+        <v>-62.59763</v>
       </c>
       <c r="X357" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K03-037</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=E07-039</t>
         </is>
       </c>
     </row>
@@ -26946,12 +26946,12 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Doyle Road North Au-Ag Occurrence</t>
+          <t>Mullach Brook Cu Occurrence</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>K07-078</t>
+          <t>K03-037</t>
         </is>
       </c>
       <c r="D359" t="inlineStr"/>
@@ -26963,12 +26963,12 @@
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>Au, Ag</t>
+          <t>Cu, As</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>Float</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="I359" t="b">
@@ -26984,7 +26984,7 @@
       </c>
       <c r="L359" t="inlineStr">
         <is>
-          <t>Au 1.15 g/t, Ag 8.20 g/t, Bi 0.00238%, Co 0.00318%, Cu 0.0036%</t>
+          <t>Cu 0.972%, Au 0.24 g/t</t>
         </is>
       </c>
       <c r="M359" t="inlineStr"/>
@@ -26996,23 +26996,23 @@
       <c r="Q359" t="inlineStr"/>
       <c r="R359" t="inlineStr"/>
       <c r="S359" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T359" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U359" t="n">
         <v>23</v>
       </c>
       <c r="V359" t="n">
-        <v>46.488</v>
+        <v>46.00426</v>
       </c>
       <c r="W359" t="n">
-        <v>-60.74453</v>
+        <v>-61.11223</v>
       </c>
       <c r="X359" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-078</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K03-037</t>
         </is>
       </c>
     </row>

--- a/site/ns_leads.xlsx
+++ b/site/ns_leads.xlsx
@@ -26262,12 +26262,12 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Goose Cove Brook   Cu, Mo Occurrence</t>
+          <t>Ingram River Cu, Sn Occurrence</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>K07-055</t>
+          <t>D12-013</t>
         </is>
       </c>
       <c r="D350" t="inlineStr"/>
@@ -26279,7 +26279,7 @@
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>Cu, Mo</t>
+          <t>Cu, Sn, Ag, Au, Bi, F, As</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
@@ -26300,7 +26300,7 @@
       </c>
       <c r="L350" t="inlineStr">
         <is>
-          <t>Mo 0.486%, Cu 0.188%, Ag 5.60 g/t, Au 0.04 g/t, Co 0.0011%</t>
+          <t>Cu 0.773%, Sn 0.162%, Ag 6.60 g/t, Mo 0.0101%, Be 0.0007%</t>
         </is>
       </c>
       <c r="M350" t="inlineStr"/>
@@ -26321,14 +26321,14 @@
         <v>25</v>
       </c>
       <c r="V350" t="n">
-        <v>46.26487</v>
+        <v>44.68634</v>
       </c>
       <c r="W350" t="n">
-        <v>-60.65547</v>
+        <v>-63.97235</v>
       </c>
       <c r="X350" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-055</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D12-013</t>
         </is>
       </c>
     </row>
@@ -26338,12 +26338,12 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Ingram River Cu, Sn Occurrence</t>
+          <t>Goose Cove Brook   Cu, Mo Occurrence</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>D12-013</t>
+          <t>K07-055</t>
         </is>
       </c>
       <c r="D351" t="inlineStr"/>
@@ -26355,7 +26355,7 @@
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>Cu, Sn, Ag, Au, Bi, F, As</t>
+          <t>Cu, Mo</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
@@ -26376,7 +26376,7 @@
       </c>
       <c r="L351" t="inlineStr">
         <is>
-          <t>Cu 0.773%, Sn 0.162%, Ag 6.60 g/t, Mo 0.0101%, Be 0.0007%</t>
+          <t>Mo 0.486%, Cu 0.188%, Ag 5.60 g/t, Au 0.04 g/t, Co 0.0011%</t>
         </is>
       </c>
       <c r="M351" t="inlineStr"/>
@@ -26394,17 +26394,17 @@
         <v>325</v>
       </c>
       <c r="U351" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V351" t="n">
-        <v>44.68634</v>
+        <v>46.26487</v>
       </c>
       <c r="W351" t="n">
-        <v>-63.97235</v>
+        <v>-60.65547</v>
       </c>
       <c r="X351" t="inlineStr">
         <is>
-          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=D12-013</t>
+          <t>https://gesner.novascotia.ca/modb/queryView/singlereport.aspx?Occ_number=K07-055</t>
         </is>
       </c>
     </row>
